--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,18 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,12 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>319</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-80</v>
+        <v>-69</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>40</v>
@@ -586,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -603,10 +585,10 @@
         <v>319</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-80</v>
+        <v>-69</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>40</v>
@@ -631,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +623,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>416</v>
+        <v>319</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1337</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-921</v>
+        <v>-69</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +668,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>745</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1337</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-592</v>
+        <v>-69</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +713,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>745</v>
+        <v>319</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1337</v>
+        <v>388</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-592</v>
+        <v>-69</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,168 +758,33 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>408</v>
+        <v>319</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1337</v>
+        <v>388</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-929</v>
+        <v>-69</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-837</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1337</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-837</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-328</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>416</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>468</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-52</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_HMB_threats.xlsx
+++ b/excel_routes/route_TUU_HMB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D64EB9-78A0-4FF5-AD56-61DB7D1737D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB40818-679B-4E3C-808B-A15C322605D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,10 +755,10 @@
         <v>397</v>
       </c>
       <c r="E8" s="2">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F8" s="2">
-        <v>-200</v>
+        <v>-229</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -790,10 +790,10 @@
         <v>397</v>
       </c>
       <c r="E9" s="2">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F9" s="2">
-        <v>-200</v>
+        <v>-229</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
